--- a/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 9/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="366" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{913731D1-470C-4441-B77D-F16BA6ED70A8}"/>
+  <xr:revisionPtr revIDLastSave="386" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9602539-AD2A-44A4-9DB8-16D751EC384B}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="40">
   <si>
     <t>Wk</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>Research: ways to implement gesture control into a simulation</t>
+  </si>
+  <si>
+    <t>Code gesture to gamepad bridge</t>
+  </si>
+  <si>
+    <t>Code gesture to gamepad bridge w/ Murphy</t>
   </si>
 </sst>
 </file>
@@ -393,6 +399,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -411,14 +425,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -512,6 +518,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -852,36 +862,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -901,7 +911,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1771,14 +1781,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2360,39 +2370,67 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B50" s="4"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="5"/>
-      <c r="G50" s="6" t="str">
+      <c r="A50" s="1">
+        <v>9</v>
+      </c>
+      <c r="B50" s="4">
+        <v>44825</v>
+      </c>
+      <c r="C50" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D50" s="4">
+        <v>44825</v>
+      </c>
+      <c r="E50" s="5">
+        <v>0.65625</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G50" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H50" s="1" t="str">
+        <v>1.7499999999417923</v>
+      </c>
+      <c r="H50" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>44.25</v>
       </c>
       <c r="I50" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1.7499999999417923</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B51" s="4"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="5"/>
-      <c r="G51" s="6" t="str">
+      <c r="A51" s="1">
+        <v>9</v>
+      </c>
+      <c r="B51" s="4">
+        <v>44826</v>
+      </c>
+      <c r="C51" s="5">
+        <v>0.3125</v>
+      </c>
+      <c r="D51" s="4">
+        <v>44826</v>
+      </c>
+      <c r="E51" s="5">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G51" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H51" s="1" t="str">
+        <v>2.0000000000582077</v>
+      </c>
+      <c r="H51" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>46.250000000058208</v>
       </c>
       <c r="I51" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.0000000000582077</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
@@ -2618,14 +2656,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -3114,14 +3152,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3608,18 +3646,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3633,6 +3659,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 9/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="386" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9602539-AD2A-44A4-9DB8-16D751EC384B}"/>
+  <xr:revisionPtr revIDLastSave="392" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FE2A101-BC84-4B22-BD7A-5DCA709620CC}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
   <si>
     <t>Wk</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>Code gesture to gamepad bridge w/ Murphy</t>
+  </si>
+  <si>
+    <t>Documentation</t>
   </si>
 </sst>
 </file>
@@ -399,14 +402,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -425,6 +420,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -862,36 +865,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -911,7 +914,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1781,14 +1784,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2434,21 +2437,35 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B52" s="4"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="5"/>
-      <c r="G52" s="6" t="str">
+      <c r="A52" s="1">
+        <v>9</v>
+      </c>
+      <c r="B52" s="4">
+        <v>44826</v>
+      </c>
+      <c r="C52" s="5">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D52" s="4">
+        <v>44826</v>
+      </c>
+      <c r="E52" s="5">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G52" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H52" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H52" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>47.000000000058208</v>
       </c>
       <c r="I52" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
@@ -2656,14 +2673,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -3152,14 +3169,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3646,6 +3663,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3659,18 +3688,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 9/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="392" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FE2A101-BC84-4B22-BD7A-5DCA709620CC}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{633229C9-3132-456E-BE54-015FD64F2232}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
   <si>
     <t>Wk</t>
   </si>
@@ -402,6 +402,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -420,14 +428,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -865,36 +865,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1784,14 +1784,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2469,21 +2469,35 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B53" s="4"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="5"/>
-      <c r="G53" s="6" t="str">
+      <c r="A53" s="1">
+        <v>9</v>
+      </c>
+      <c r="B53" s="4">
+        <v>44826</v>
+      </c>
+      <c r="C53" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D53" s="4">
+        <v>44826</v>
+      </c>
+      <c r="E53" s="5">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H53" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H53" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>47.750000000058208</v>
       </c>
       <c r="I53" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
@@ -2673,14 +2687,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -3169,14 +3183,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3663,18 +3677,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3688,6 +3690,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 9/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="398" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{633229C9-3132-456E-BE54-015FD64F2232}"/>
+  <xr:revisionPtr revIDLastSave="404" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A28DBF-8DAE-4BEB-A0B2-5990C370E145}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23664" yWindow="624" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
   <si>
     <t>Wk</t>
   </si>
@@ -402,14 +402,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -428,6 +420,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -850,55 +850,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.08984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.6328125" style="1"/>
+    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
-    </row>
-    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -914,7 +914,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1780,18 +1780,18 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
@@ -2501,21 +2501,35 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B54" s="4"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="5"/>
-      <c r="G54" s="6" t="str">
+      <c r="A54" s="1">
+        <v>9</v>
+      </c>
+      <c r="B54" s="4">
+        <v>44826</v>
+      </c>
+      <c r="C54" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D54" s="4">
+        <v>44826</v>
+      </c>
+      <c r="E54" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H54" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H54" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>48.250000000116415</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.50000000005820766</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
@@ -2683,18 +2697,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2709,7 +2723,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
@@ -3179,18 +3193,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3205,7 +3219,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
@@ -3677,6 +3691,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3690,18 +3716,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -3713,7 +3727,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3725,7 +3739,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 9/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="404" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A28DBF-8DAE-4BEB-A0B2-5990C370E145}"/>
+  <xr:revisionPtr revIDLastSave="410" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4C1635-7653-4613-9CE6-80F61CFE5A42}"/>
   <bookViews>
     <workbookView xWindow="23664" yWindow="624" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="42">
   <si>
     <t>Wk</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>Documentation</t>
+  </si>
+  <si>
+    <t>Person ID code testing and debugging</t>
   </si>
 </sst>
 </file>
@@ -402,6 +405,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -420,14 +431,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -865,36 +868,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -914,7 +917,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1784,14 +1787,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2533,21 +2536,35 @@
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B55" s="4"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="5"/>
-      <c r="G55" s="6" t="str">
+      <c r="A55" s="1">
+        <v>9</v>
+      </c>
+      <c r="B55" s="4">
+        <v>44827</v>
+      </c>
+      <c r="C55" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D55" s="4">
+        <v>44827</v>
+      </c>
+      <c r="E55" s="5">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H55" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H55" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>49.000000000116415</v>
       </c>
       <c r="I55" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
@@ -2701,14 +2718,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -3197,14 +3214,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3691,18 +3708,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3716,6 +3721,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 9/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="410" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F4C1635-7653-4613-9CE6-80F61CFE5A42}"/>
+  <xr:revisionPtr revIDLastSave="422" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15618014-B7D9-4F8E-A1CF-471B470C61F1}"/>
   <bookViews>
-    <workbookView xWindow="23664" yWindow="624" windowWidth="17280" windowHeight="9960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15420" yWindow="-3390" windowWidth="12150" windowHeight="20685" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="42">
   <si>
     <t>Wk</t>
   </si>
@@ -405,14 +405,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -431,6 +423,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -868,36 +868,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1787,14 +1787,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2568,39 +2568,67 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B56" s="4"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="5"/>
-      <c r="G56" s="6" t="str">
+      <c r="A56" s="1">
+        <v>9</v>
+      </c>
+      <c r="B56" s="4">
+        <v>44828</v>
+      </c>
+      <c r="C56" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="D56" s="4">
+        <v>44828</v>
+      </c>
+      <c r="E56" s="5">
+        <v>0.40625</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H56" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H56" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>49.750000000116415</v>
       </c>
       <c r="I56" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B57" s="4"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="5"/>
-      <c r="G57" s="6" t="str">
+      <c r="A57" s="1">
+        <v>9</v>
+      </c>
+      <c r="B57" s="4">
+        <v>44828</v>
+      </c>
+      <c r="C57" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D57" s="4">
+        <v>44828</v>
+      </c>
+      <c r="E57" s="5">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H57" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H57" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>50.500000000116415</v>
       </c>
       <c r="I57" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
@@ -2718,14 +2746,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -3214,14 +3242,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3708,6 +3736,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3721,18 +3761,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 9/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 9/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="422" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15618014-B7D9-4F8E-A1CF-471B470C61F1}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BCD1D8B-CD1C-41F0-A0D6-2620ED04675C}"/>
   <bookViews>
     <workbookView xWindow="-15420" yWindow="-3390" windowWidth="12150" windowHeight="20685" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
   <si>
     <t>Wk</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>Person ID code testing and debugging</t>
+  </si>
+  <si>
+    <t>Recording Demo for Client (Documentation)</t>
   </si>
 </sst>
 </file>
@@ -405,6 +408,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -423,14 +434,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -868,36 +871,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -917,7 +920,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1787,14 +1790,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2632,21 +2635,35 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B58" s="4"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="5"/>
-      <c r="G58" s="6" t="str">
+      <c r="A58" s="1">
+        <v>9</v>
+      </c>
+      <c r="B58" s="4">
+        <v>44828</v>
+      </c>
+      <c r="C58" s="5">
+        <v>0.53125</v>
+      </c>
+      <c r="D58" s="4">
+        <v>44828</v>
+      </c>
+      <c r="E58" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H58" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H58" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>51.250000000116415</v>
       </c>
       <c r="I58" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
@@ -2746,14 +2763,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -3242,14 +3259,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3736,18 +3753,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3761,6 +3766,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
